--- a/PK/Exp2025-FashionMNIST-Dir0.1/cnn-dir0.1baseline_300.xlsx
+++ b/PK/Exp2025-FashionMNIST-Dir0.1/cnn-dir0.1baseline_300.xlsx
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(0.1)</t>
+          <t>nonIID(plus3)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D3" t="n">
-        <v>11.88</v>
+        <v>18.85</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>20.12</v>
+        <v>33.73</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="J3" t="n">
-        <v>84.3</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="4">

--- a/PK/Exp2025-FashionMNIST-Dir0.1/cnn-dir0.1baseline_300.xlsx
+++ b/PK/Exp2025-FashionMNIST-Dir0.1/cnn-dir0.1baseline_300.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>7.24</v>
+        <v>5.64</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>15.77</v>
+        <v>12.37</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>26.97</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>34.43</v>
       </c>
       <c r="J2" t="n">
-        <v>84.68000000000001</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(plus3)</t>
+          <t>nonIID(0.1)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="D3" t="n">
-        <v>18.85</v>
+        <v>11.88</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>33.73</v>
+        <v>20.12</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="J3" t="n">
-        <v>83.13</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="4">
@@ -596,20 +596,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>TiFL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>17.08</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="F5" t="n">
-        <v>29.78</v>
+        <v>15.91</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>54.9</v>
+        <v>33.56</v>
       </c>
       <c r="J5" t="n">
-        <v>83.68000000000001</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="6">
